--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000594</v>
+        <v>129000596</v>
       </c>
       <c r="B7" t="n">
-        <v>92823</v>
+        <v>92849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729259</v>
+        <v>729217</v>
       </c>
       <c r="R7" t="n">
-        <v>7331864</v>
+        <v>7331837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000596</v>
+        <v>129000594</v>
       </c>
       <c r="B8" t="n">
-        <v>92849</v>
+        <v>92823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729217</v>
+        <v>729259</v>
       </c>
       <c r="R8" t="n">
-        <v>7331837</v>
+        <v>7331864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000588</v>
       </c>
       <c r="B2" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129000591</v>
       </c>
       <c r="B4" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129000589</v>
       </c>
       <c r="B5" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129000583</v>
       </c>
       <c r="B6" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000596</v>
+        <v>129000594</v>
       </c>
       <c r="B7" t="n">
-        <v>92849</v>
+        <v>92828</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729217</v>
+        <v>729259</v>
       </c>
       <c r="R7" t="n">
-        <v>7331837</v>
+        <v>7331864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000594</v>
+        <v>129000596</v>
       </c>
       <c r="B8" t="n">
-        <v>92823</v>
+        <v>92854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729259</v>
+        <v>729217</v>
       </c>
       <c r="R8" t="n">
-        <v>7331864</v>
+        <v>7331837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1526,7 +1526,7 @@
         <v>129000590</v>
       </c>
       <c r="B10" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000588</v>
       </c>
       <c r="B2" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000582</v>
+        <v>129000591</v>
       </c>
       <c r="B3" t="n">
-        <v>78791</v>
+        <v>97536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729100</v>
+        <v>729673</v>
       </c>
       <c r="R3" t="n">
-        <v>7331636</v>
+        <v>7331472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000591</v>
+        <v>129000582</v>
       </c>
       <c r="B4" t="n">
-        <v>97533</v>
+        <v>78792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729673</v>
+        <v>729100</v>
       </c>
       <c r="R4" t="n">
-        <v>7331472</v>
+        <v>7331636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000589</v>
+        <v>129000583</v>
       </c>
       <c r="B5" t="n">
-        <v>92816</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729145</v>
+        <v>729389</v>
       </c>
       <c r="R5" t="n">
-        <v>7331788</v>
+        <v>7331590</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000583</v>
+        <v>129000589</v>
       </c>
       <c r="B6" t="n">
-        <v>92854</v>
+        <v>92819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729389</v>
+        <v>729145</v>
       </c>
       <c r="R6" t="n">
-        <v>7331590</v>
+        <v>7331788</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
         <v>129000594</v>
       </c>
       <c r="B7" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>129000596</v>
       </c>
       <c r="B8" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>129000595</v>
       </c>
       <c r="B9" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129000590</v>
       </c>
       <c r="B10" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000591</v>
+        <v>129000582</v>
       </c>
       <c r="B3" t="n">
-        <v>97536</v>
+        <v>78792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729673</v>
+        <v>729100</v>
       </c>
       <c r="R3" t="n">
-        <v>7331472</v>
+        <v>7331636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000582</v>
+        <v>129000591</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>97536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729100</v>
+        <v>729673</v>
       </c>
       <c r="R4" t="n">
-        <v>7331636</v>
+        <v>7331472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000583</v>
+        <v>129000589</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92819</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729389</v>
+        <v>729145</v>
       </c>
       <c r="R5" t="n">
-        <v>7331590</v>
+        <v>7331788</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000589</v>
+        <v>129000583</v>
       </c>
       <c r="B6" t="n">
-        <v>92819</v>
+        <v>92857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729145</v>
+        <v>729389</v>
       </c>
       <c r="R6" t="n">
-        <v>7331788</v>
+        <v>7331590</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000582</v>
+        <v>129000591</v>
       </c>
       <c r="B3" t="n">
-        <v>78792</v>
+        <v>97536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729100</v>
+        <v>729673</v>
       </c>
       <c r="R3" t="n">
-        <v>7331636</v>
+        <v>7331472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000591</v>
+        <v>129000582</v>
       </c>
       <c r="B4" t="n">
-        <v>97536</v>
+        <v>78792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729673</v>
+        <v>729100</v>
       </c>
       <c r="R4" t="n">
-        <v>7331472</v>
+        <v>7331636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000589</v>
+        <v>129000583</v>
       </c>
       <c r="B5" t="n">
-        <v>92819</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729145</v>
+        <v>729389</v>
       </c>
       <c r="R5" t="n">
-        <v>7331788</v>
+        <v>7331590</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000583</v>
+        <v>129000589</v>
       </c>
       <c r="B6" t="n">
-        <v>92857</v>
+        <v>92819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729389</v>
+        <v>729145</v>
       </c>
       <c r="R6" t="n">
-        <v>7331590</v>
+        <v>7331788</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000594</v>
+        <v>129000596</v>
       </c>
       <c r="B7" t="n">
-        <v>92831</v>
+        <v>92857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729259</v>
+        <v>729217</v>
       </c>
       <c r="R7" t="n">
-        <v>7331864</v>
+        <v>7331837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000596</v>
+        <v>129000594</v>
       </c>
       <c r="B8" t="n">
-        <v>92857</v>
+        <v>92831</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729217</v>
+        <v>729259</v>
       </c>
       <c r="R8" t="n">
-        <v>7331837</v>
+        <v>7331864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000588</v>
       </c>
       <c r="B2" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000591</v>
       </c>
       <c r="B3" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129000582</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129000583</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129000589</v>
       </c>
       <c r="B6" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000596</v>
+        <v>129000594</v>
       </c>
       <c r="B7" t="n">
-        <v>92857</v>
+        <v>92838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729217</v>
+        <v>729259</v>
       </c>
       <c r="R7" t="n">
-        <v>7331837</v>
+        <v>7331864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000594</v>
+        <v>129000596</v>
       </c>
       <c r="B8" t="n">
-        <v>92831</v>
+        <v>92864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729259</v>
+        <v>729217</v>
       </c>
       <c r="R8" t="n">
-        <v>7331864</v>
+        <v>7331837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1420,7 @@
         <v>129000595</v>
       </c>
       <c r="B9" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129000590</v>
       </c>
       <c r="B10" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000588</v>
       </c>
       <c r="B2" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000591</v>
+        <v>129000582</v>
       </c>
       <c r="B3" t="n">
-        <v>97546</v>
+        <v>78796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729673</v>
+        <v>729100</v>
       </c>
       <c r="R3" t="n">
-        <v>7331472</v>
+        <v>7331636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000582</v>
+        <v>129000591</v>
       </c>
       <c r="B4" t="n">
-        <v>78796</v>
+        <v>97553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729100</v>
+        <v>729673</v>
       </c>
       <c r="R4" t="n">
-        <v>7331636</v>
+        <v>7331472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000583</v>
+        <v>129000589</v>
       </c>
       <c r="B5" t="n">
-        <v>92864</v>
+        <v>92833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729389</v>
+        <v>729145</v>
       </c>
       <c r="R5" t="n">
-        <v>7331590</v>
+        <v>7331788</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000589</v>
+        <v>129000583</v>
       </c>
       <c r="B6" t="n">
-        <v>92826</v>
+        <v>92871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729145</v>
+        <v>729389</v>
       </c>
       <c r="R6" t="n">
-        <v>7331788</v>
+        <v>7331590</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
         <v>129000594</v>
       </c>
       <c r="B7" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>129000596</v>
       </c>
       <c r="B8" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129000590</v>
       </c>
       <c r="B10" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000588</v>
       </c>
       <c r="B2" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000582</v>
       </c>
       <c r="B3" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129000591</v>
       </c>
       <c r="B4" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000589</v>
+        <v>129000583</v>
       </c>
       <c r="B5" t="n">
-        <v>92833</v>
+        <v>92873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729145</v>
+        <v>729389</v>
       </c>
       <c r="R5" t="n">
-        <v>7331788</v>
+        <v>7331590</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000583</v>
+        <v>129000589</v>
       </c>
       <c r="B6" t="n">
-        <v>92871</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729389</v>
+        <v>729145</v>
       </c>
       <c r="R6" t="n">
-        <v>7331590</v>
+        <v>7331788</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000594</v>
+        <v>129000596</v>
       </c>
       <c r="B7" t="n">
-        <v>92845</v>
+        <v>92873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729259</v>
+        <v>729217</v>
       </c>
       <c r="R7" t="n">
-        <v>7331864</v>
+        <v>7331837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000596</v>
+        <v>129000594</v>
       </c>
       <c r="B8" t="n">
-        <v>92871</v>
+        <v>92847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729217</v>
+        <v>729259</v>
       </c>
       <c r="R8" t="n">
-        <v>7331837</v>
+        <v>7331864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1420,7 @@
         <v>129000595</v>
       </c>
       <c r="B9" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129000590</v>
       </c>
       <c r="B10" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000583</v>
+        <v>129000589</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729389</v>
+        <v>729145</v>
       </c>
       <c r="R5" t="n">
-        <v>7331590</v>
+        <v>7331788</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000589</v>
+        <v>129000583</v>
       </c>
       <c r="B6" t="n">
-        <v>92835</v>
+        <v>92873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729145</v>
+        <v>729389</v>
       </c>
       <c r="R6" t="n">
-        <v>7331788</v>
+        <v>7331590</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000596</v>
+        <v>129000594</v>
       </c>
       <c r="B7" t="n">
-        <v>92873</v>
+        <v>92847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729217</v>
+        <v>729259</v>
       </c>
       <c r="R7" t="n">
-        <v>7331837</v>
+        <v>7331864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000594</v>
+        <v>129000596</v>
       </c>
       <c r="B8" t="n">
-        <v>92847</v>
+        <v>92873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729259</v>
+        <v>729217</v>
       </c>
       <c r="R8" t="n">
-        <v>7331864</v>
+        <v>7331837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000582</v>
+        <v>129000591</v>
       </c>
       <c r="B3" t="n">
-        <v>78798</v>
+        <v>97555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729100</v>
+        <v>729673</v>
       </c>
       <c r="R3" t="n">
-        <v>7331636</v>
+        <v>7331472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000591</v>
+        <v>129000582</v>
       </c>
       <c r="B4" t="n">
-        <v>97555</v>
+        <v>78798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729673</v>
+        <v>729100</v>
       </c>
       <c r="R4" t="n">
-        <v>7331472</v>
+        <v>7331636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000588</v>
       </c>
       <c r="B2" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000591</v>
+        <v>129000582</v>
       </c>
       <c r="B3" t="n">
-        <v>97555</v>
+        <v>78798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729673</v>
+        <v>729100</v>
       </c>
       <c r="R3" t="n">
-        <v>7331472</v>
+        <v>7331636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000582</v>
+        <v>129000591</v>
       </c>
       <c r="B4" t="n">
-        <v>78798</v>
+        <v>97581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729100</v>
+        <v>729673</v>
       </c>
       <c r="R4" t="n">
-        <v>7331636</v>
+        <v>7331472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000589</v>
+        <v>129000583</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>92859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729145</v>
+        <v>729389</v>
       </c>
       <c r="R5" t="n">
-        <v>7331788</v>
+        <v>7331590</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000583</v>
+        <v>129000589</v>
       </c>
       <c r="B6" t="n">
-        <v>92873</v>
+        <v>92821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729389</v>
+        <v>729145</v>
       </c>
       <c r="R6" t="n">
-        <v>7331590</v>
+        <v>7331788</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
         <v>129000594</v>
       </c>
       <c r="B7" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>129000596</v>
       </c>
       <c r="B8" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129000590</v>
       </c>
       <c r="B10" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000588</v>
       </c>
       <c r="B2" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129000591</v>
       </c>
       <c r="B4" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129000583</v>
       </c>
       <c r="B5" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129000589</v>
       </c>
       <c r="B6" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000594</v>
+        <v>129000596</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729259</v>
+        <v>729217</v>
       </c>
       <c r="R7" t="n">
-        <v>7331864</v>
+        <v>7331837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000596</v>
+        <v>129000594</v>
       </c>
       <c r="B8" t="n">
-        <v>92859</v>
+        <v>92834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729217</v>
+        <v>729259</v>
       </c>
       <c r="R8" t="n">
-        <v>7331837</v>
+        <v>7331864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1526,7 +1526,7 @@
         <v>129000590</v>
       </c>
       <c r="B10" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129000591</v>
       </c>
       <c r="B4" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000588</v>
       </c>
       <c r="B2" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000582</v>
+        <v>129000591</v>
       </c>
       <c r="B3" t="n">
-        <v>78798</v>
+        <v>97587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729100</v>
+        <v>729673</v>
       </c>
       <c r="R3" t="n">
-        <v>7331636</v>
+        <v>7331472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000591</v>
+        <v>129000582</v>
       </c>
       <c r="B4" t="n">
-        <v>97583</v>
+        <v>78800</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729673</v>
+        <v>729100</v>
       </c>
       <c r="R4" t="n">
-        <v>7331472</v>
+        <v>7331636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000583</v>
+        <v>129000589</v>
       </c>
       <c r="B5" t="n">
-        <v>92860</v>
+        <v>92825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729389</v>
+        <v>729145</v>
       </c>
       <c r="R5" t="n">
-        <v>7331590</v>
+        <v>7331788</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000589</v>
+        <v>129000583</v>
       </c>
       <c r="B6" t="n">
-        <v>92822</v>
+        <v>92863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729145</v>
+        <v>729389</v>
       </c>
       <c r="R6" t="n">
-        <v>7331788</v>
+        <v>7331590</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000596</v>
+        <v>129000594</v>
       </c>
       <c r="B7" t="n">
-        <v>92860</v>
+        <v>92837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729217</v>
+        <v>729259</v>
       </c>
       <c r="R7" t="n">
-        <v>7331837</v>
+        <v>7331864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000594</v>
+        <v>129000596</v>
       </c>
       <c r="B8" t="n">
-        <v>92834</v>
+        <v>92863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729259</v>
+        <v>729217</v>
       </c>
       <c r="R8" t="n">
-        <v>7331864</v>
+        <v>7331837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1420,7 @@
         <v>129000595</v>
       </c>
       <c r="B9" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129000590</v>
       </c>
       <c r="B10" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000591</v>
+        <v>129000582</v>
       </c>
       <c r="B3" t="n">
-        <v>97587</v>
+        <v>78800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729673</v>
+        <v>729100</v>
       </c>
       <c r="R3" t="n">
-        <v>7331472</v>
+        <v>7331636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000582</v>
+        <v>129000591</v>
       </c>
       <c r="B4" t="n">
-        <v>78800</v>
+        <v>97587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729100</v>
+        <v>729673</v>
       </c>
       <c r="R4" t="n">
-        <v>7331636</v>
+        <v>7331472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000588</v>
       </c>
       <c r="B2" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000582</v>
       </c>
       <c r="B3" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129000591</v>
       </c>
       <c r="B4" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000589</v>
+        <v>129000583</v>
       </c>
       <c r="B5" t="n">
-        <v>92825</v>
+        <v>92865</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729145</v>
+        <v>729389</v>
       </c>
       <c r="R5" t="n">
-        <v>7331788</v>
+        <v>7331590</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000583</v>
+        <v>129000589</v>
       </c>
       <c r="B6" t="n">
-        <v>92863</v>
+        <v>92827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729389</v>
+        <v>729145</v>
       </c>
       <c r="R6" t="n">
-        <v>7331590</v>
+        <v>7331788</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
         <v>129000594</v>
       </c>
       <c r="B7" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>129000596</v>
       </c>
       <c r="B8" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>129000595</v>
       </c>
       <c r="B9" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129000590</v>
       </c>
       <c r="B10" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000588</v>
       </c>
       <c r="B2" t="n">
-        <v>92831</v>
+        <v>92835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129000591</v>
       </c>
       <c r="B4" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000583</v>
+        <v>129000589</v>
       </c>
       <c r="B5" t="n">
-        <v>92865</v>
+        <v>92831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729389</v>
+        <v>729145</v>
       </c>
       <c r="R5" t="n">
-        <v>7331590</v>
+        <v>7331788</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000589</v>
+        <v>129000583</v>
       </c>
       <c r="B6" t="n">
-        <v>92827</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729145</v>
+        <v>729389</v>
       </c>
       <c r="R6" t="n">
-        <v>7331788</v>
+        <v>7331590</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
         <v>129000594</v>
       </c>
       <c r="B7" t="n">
-        <v>92839</v>
+        <v>92843</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>129000596</v>
       </c>
       <c r="B8" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129000590</v>
       </c>
       <c r="B10" t="n">
-        <v>92839</v>
+        <v>92843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000588</v>
       </c>
       <c r="B2" t="n">
-        <v>92835</v>
+        <v>92836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129000591</v>
       </c>
       <c r="B4" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129000589</v>
       </c>
       <c r="B5" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129000583</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000594</v>
+        <v>129000596</v>
       </c>
       <c r="B7" t="n">
-        <v>92843</v>
+        <v>92870</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729259</v>
+        <v>729217</v>
       </c>
       <c r="R7" t="n">
-        <v>7331864</v>
+        <v>7331837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000596</v>
+        <v>129000594</v>
       </c>
       <c r="B8" t="n">
-        <v>92869</v>
+        <v>92844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729217</v>
+        <v>729259</v>
       </c>
       <c r="R8" t="n">
-        <v>7331837</v>
+        <v>7331864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1526,7 +1526,7 @@
         <v>129000590</v>
       </c>
       <c r="B10" t="n">
-        <v>92843</v>
+        <v>92844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000582</v>
+        <v>129000591</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>97601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729100</v>
+        <v>729673</v>
       </c>
       <c r="R3" t="n">
-        <v>7331636</v>
+        <v>7331472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000591</v>
+        <v>129000582</v>
       </c>
       <c r="B4" t="n">
-        <v>97601</v>
+        <v>78801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729673</v>
+        <v>729100</v>
       </c>
       <c r="R4" t="n">
-        <v>7331472</v>
+        <v>7331636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000589</v>
+        <v>129000583</v>
       </c>
       <c r="B5" t="n">
-        <v>92832</v>
+        <v>92870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729145</v>
+        <v>729389</v>
       </c>
       <c r="R5" t="n">
-        <v>7331788</v>
+        <v>7331590</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000583</v>
+        <v>129000589</v>
       </c>
       <c r="B6" t="n">
-        <v>92870</v>
+        <v>92832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729389</v>
+        <v>729145</v>
       </c>
       <c r="R6" t="n">
-        <v>7331590</v>
+        <v>7331788</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000596</v>
+        <v>129000594</v>
       </c>
       <c r="B7" t="n">
-        <v>92870</v>
+        <v>92844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729217</v>
+        <v>729259</v>
       </c>
       <c r="R7" t="n">
-        <v>7331837</v>
+        <v>7331864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000594</v>
+        <v>129000596</v>
       </c>
       <c r="B8" t="n">
-        <v>92844</v>
+        <v>92870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729259</v>
+        <v>729217</v>
       </c>
       <c r="R8" t="n">
-        <v>7331864</v>
+        <v>7331837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000591</v>
+        <v>129000582</v>
       </c>
       <c r="B3" t="n">
-        <v>97601</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729673</v>
+        <v>729100</v>
       </c>
       <c r="R3" t="n">
-        <v>7331472</v>
+        <v>7331636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000582</v>
+        <v>129000591</v>
       </c>
       <c r="B4" t="n">
-        <v>78801</v>
+        <v>97601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729100</v>
+        <v>729673</v>
       </c>
       <c r="R4" t="n">
-        <v>7331636</v>
+        <v>7331472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000588</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>92839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129000591</v>
       </c>
       <c r="B4" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000583</v>
+        <v>129000589</v>
       </c>
       <c r="B5" t="n">
-        <v>92870</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729389</v>
+        <v>729145</v>
       </c>
       <c r="R5" t="n">
-        <v>7331590</v>
+        <v>7331788</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000589</v>
+        <v>129000583</v>
       </c>
       <c r="B6" t="n">
-        <v>92832</v>
+        <v>92873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729145</v>
+        <v>729389</v>
       </c>
       <c r="R6" t="n">
-        <v>7331788</v>
+        <v>7331590</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
         <v>129000594</v>
       </c>
       <c r="B7" t="n">
-        <v>92844</v>
+        <v>92847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>129000596</v>
       </c>
       <c r="B8" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129000590</v>
       </c>
       <c r="B10" t="n">
-        <v>92844</v>
+        <v>92847</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129000588</v>
+        <v>129000584</v>
       </c>
       <c r="B2" t="n">
-        <v>92839</v>
+        <v>91394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>2051</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729294</v>
+        <v>729388</v>
       </c>
       <c r="R2" t="n">
-        <v>7331886</v>
+        <v>7331582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000582</v>
+        <v>129000589</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729100</v>
+        <v>729145</v>
       </c>
       <c r="R3" t="n">
-        <v>7331636</v>
+        <v>7331788</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000591</v>
+        <v>129000588</v>
       </c>
       <c r="B4" t="n">
-        <v>97604</v>
+        <v>93201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729673</v>
+        <v>729294</v>
       </c>
       <c r="R4" t="n">
-        <v>7331472</v>
+        <v>7331886</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000589</v>
+        <v>129000590</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729145</v>
+        <v>729137</v>
       </c>
       <c r="R5" t="n">
-        <v>7331788</v>
+        <v>7331783</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000583</v>
+        <v>129000594</v>
       </c>
       <c r="B6" t="n">
-        <v>92873</v>
+        <v>93209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729389</v>
+        <v>729259</v>
       </c>
       <c r="R6" t="n">
-        <v>7331590</v>
+        <v>7331864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000594</v>
+        <v>129000583</v>
       </c>
       <c r="B7" t="n">
-        <v>92847</v>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729259</v>
+        <v>729389</v>
       </c>
       <c r="R7" t="n">
-        <v>7331864</v>
+        <v>7331590</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1314,7 +1314,7 @@
         <v>129000596</v>
       </c>
       <c r="B8" t="n">
-        <v>92873</v>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129000595</v>
+        <v>129000582</v>
       </c>
       <c r="B9" t="n">
-        <v>78801</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729233</v>
+        <v>729100</v>
       </c>
       <c r="R9" t="n">
-        <v>7331838</v>
+        <v>7331636</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1523,32 +1523,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129000590</v>
+        <v>129000593</v>
       </c>
       <c r="B10" t="n">
-        <v>92847</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729137</v>
+        <v>729268</v>
       </c>
       <c r="R10" t="n">
-        <v>7331783</v>
+        <v>7331665</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1626,6 +1626,218 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129000595</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>729233</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7331838</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129000591</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>729673</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7331472</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49857-2025 artfynd.xlsx
+++ b/artfynd/A 49857-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000584</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000589</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000588</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000590</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000594</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000583</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000596</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000582</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000593</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000595</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,8 +1893,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000591</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>